--- a/ch_11_ai_assistance/ch_11_solutions.xlsx
+++ b/ch_11_ai_assistance/ch_11_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_11_ai_assistance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_11_ai_assistance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91142F71-92E9-472C-9A2B-02341390E24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7619A3FC-488E-418D-9C04-DA4FAFA1CCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
+          <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
@@ -72,7 +72,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -88,7 +88,21 @@
   </environmentDefinition>
   <pythonScripts>
     <pythonScript>
-      <code>mpg_df = xl(%P2%, headers=True)</code>
+      <code xml:space="preserve">mpg_df = xl(%P2%, headers=True)
+mpg_df.groupby('origin')['mpg'].agg( ['count', 'mean', 'std']).round(2) </code>
+    </pythonScript>
+    <pythonScript>
+      <code>import statsmodels.api as sm 
+df = mpg_df.copy() 
+df['origin'] = df['origin'].map( 
+    {'usa': 1, 'europe': 2, 'japan': 3}) 
+X = df[['cylinders', 'displacement', 'horsepower', 
+        'weight', 'acceleration', 'origin']] 
+y = df['mpg'] 
+X = sm.add_constant(X) 
+model = sm.OLS(y, X, missing='drop').fit() 
+model.summary() 
+f"Rows in data: {len(mpg_df):,} / Rows used by model: {int(model.nobs):,}"</code>
     </pythonScript>
   </pythonScripts>
 </python>
@@ -163,8 +177,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -222,159 +239,26 @@
 </rvTypesInfo>
 </file>
 
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <a r="12" c="9">
-    <v t="s"/>
-    <v t="s">mpg</v>
-    <v t="s">cylinders</v>
-    <v t="s">displacement</v>
-    <v t="s">horsepower</v>
-    <v t="s">weight</v>
-    <v t="s">acceleration</v>
-    <v t="s">model_year</v>
-    <v t="s">origin</v>
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <fb t="s">Rows in data: 398 / Rows used by model: 392</fb>
+    <v>&lt;class 'str'&gt;</v>
+    <v>str</v>
+    <v>Rows in data: 398 / Rows used by model: 392</v>
+    <v>Rows in data: 398 / Rows used by model: 392</v>
     <v>0</v>
-    <v>18</v>
-    <v>8</v>
-    <v>307</v>
-    <v>130</v>
-    <v>3504</v>
-    <v>12</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v>1</v>
-    <v>15</v>
-    <v>8</v>
-    <v>350</v>
-    <v>165</v>
-    <v>3693</v>
-    <v>11.5</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v>2</v>
-    <v>18</v>
-    <v>8</v>
-    <v>318</v>
-    <v>150</v>
-    <v>3436</v>
-    <v>11</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v>3</v>
-    <v>16</v>
-    <v>8</v>
-    <v>304</v>
-    <v>150</v>
-    <v>3433</v>
-    <v>12</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v>4</v>
-    <v>17</v>
-    <v>8</v>
-    <v>302</v>
-    <v>140</v>
-    <v>3449</v>
-    <v>10.5</v>
-    <v>70</v>
-    <v t="s">usa</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v>393</v>
-    <v>27</v>
-    <v>4</v>
-    <v>140</v>
-    <v>86</v>
-    <v>2790</v>
-    <v>15.6</v>
-    <v>82</v>
-    <v t="s">usa</v>
-    <v>394</v>
-    <v>44</v>
-    <v>4</v>
-    <v>97</v>
-    <v>52</v>
-    <v>2130</v>
-    <v>24.6</v>
-    <v>82</v>
-    <v t="s">europe</v>
-    <v>395</v>
-    <v>32</v>
-    <v>4</v>
-    <v>135</v>
-    <v>84</v>
-    <v>2295</v>
-    <v>11.6</v>
-    <v>82</v>
-    <v t="s">usa</v>
-    <v>396</v>
-    <v>28</v>
-    <v>4</v>
-    <v>120</v>
-    <v>79</v>
-    <v>2625</v>
-    <v>18.600000000000001</v>
-    <v>82</v>
-    <v t="s">usa</v>
-    <v>397</v>
-    <v>31</v>
-    <v>4</v>
-    <v>119</v>
-    <v>82</v>
-    <v>2720</v>
-    <v>19.399999999999999</v>
-    <v>82</v>
-    <v t="s">usa</v>
-  </a>
-</arrayData>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <rv s="0">
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>DataFrame</v>
-    <v>1</v>
-    <v>0</v>
-  </rv>
-  <rv s="2">
-    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
-    <v>DataFrame</v>
-    <v xml:space="preserve">      mpg  cylinders  displacement  horsepower  weight  acceleration  \
-0    18.0          8         307.0       130.0    3504          12.0   
-1    15.0          8         350.0       165.0    3693          11.5   
-2    18.0          8         318.0  ...</v>
-    <v>1</v>
-    <v>2</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <s t="_array">
-    <k n="array" t="a"/>
-  </s>
-  <s t="_entity">
-    <k n="_DisplayString" t="s"/>
-    <k n="_ViewInfo" t="spb"/>
-    <k n="arrayPreview" t="r"/>
-  </s>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
   <s t="_python">
     <k n="Python_type" t="s"/>
     <k n="Python_typeName" t="s"/>
     <k n="Python_str" t="s"/>
-    <k n="preview" t="r"/>
+    <k n="basicValue" t="s"/>
     <k n="_Provider" t="spb"/>
   </s>
 </rvStructures>
@@ -382,18 +266,8 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="3">
+  <spbData count="1">
     <spb s="0">
-      <v>398</v>
-      <v>8</v>
-      <v>DataFrame</v>
-      <v>arrayPreview</v>
-      <v>1</v>
-    </spb>
-    <spb s="1">
-      <v>0</v>
-    </spb>
-    <spb s="2">
       <v>https://www.anaconda.com/excel</v>
       <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
       <v>Python provided by Anaconda</v>
@@ -403,17 +277,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="3">
-  <s>
-    <k n="drw" t="i"/>
-    <k n="dcol" t="i"/>
-    <k n="name" t="s"/>
-    <k n="array" t="s"/>
-    <k n="headers" t="b"/>
-  </s>
-  <s>
-    <k n="ArrayCardInfo" t="spb"/>
-  </s>
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
   <s>
     <k n="link" t="s"/>
     <k n="logo" t="s"/>
@@ -724,20 +588,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J399"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:M399"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.1171875" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" customWidth="1"/>
-    <col min="5" max="5" width="8.1171875" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="8.1328125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.234375" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="10" max="10" width="21.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>18</v>
       </c>
@@ -788,12 +653,21 @@
       <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" t="e" cm="1" vm="1">
-        <f t="array" ref="J2">_xlfn._xlws.PY(0,1,mpg[#All])</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J2" s="1" t="str" cm="1">
+        <f t="array" ref="J2:M6">_xlfn._xlws.PY(0,0,mpg[#All])</f>
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>count</v>
+      </c>
+      <c r="L2" t="str">
+        <v>mean</v>
+      </c>
+      <c r="M2" t="str">
+        <v>std</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>15</v>
       </c>
@@ -818,8 +692,20 @@
       <c r="H3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J3" t="str">
+        <v>origin</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>18</v>
       </c>
@@ -844,8 +730,20 @@
       <c r="H4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J4" t="str">
+        <v>europe</v>
+      </c>
+      <c r="K4">
+        <v>70</v>
+      </c>
+      <c r="L4">
+        <v>27.89</v>
+      </c>
+      <c r="M4">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>16</v>
       </c>
@@ -870,8 +768,20 @@
       <c r="H5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J5" t="str">
+        <v>japan</v>
+      </c>
+      <c r="K5">
+        <v>79</v>
+      </c>
+      <c r="L5">
+        <v>30.45</v>
+      </c>
+      <c r="M5">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>17</v>
       </c>
@@ -896,8 +806,20 @@
       <c r="H6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J6" t="str">
+        <v>usa</v>
+      </c>
+      <c r="K6">
+        <v>249</v>
+      </c>
+      <c r="L6">
+        <v>20.079999999999998</v>
+      </c>
+      <c r="M6">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>15</v>
       </c>
@@ -923,7 +845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>14</v>
       </c>
@@ -949,7 +871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>14</v>
       </c>
@@ -974,8 +896,12 @@
       <c r="H9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J9" t="str" cm="1" vm="1">
+        <f t="array" ref="J9">_xlfn._xlws.PY(1,1)</f>
+        <v>Rows in data: 398 / Rows used by model: 392</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>14</v>
       </c>
@@ -1001,7 +927,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>15</v>
       </c>
@@ -1027,7 +953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>15</v>
       </c>
@@ -1053,7 +979,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>14</v>
       </c>
@@ -1079,7 +1005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>15</v>
       </c>
@@ -1105,7 +1031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1131,7 +1057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>24</v>
       </c>
@@ -1157,7 +1083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>22</v>
       </c>
@@ -1183,7 +1109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>18</v>
       </c>
@@ -1209,7 +1135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>21</v>
       </c>
@@ -1235,7 +1161,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>27</v>
       </c>
@@ -1261,7 +1187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>26</v>
       </c>
@@ -1287,7 +1213,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>25</v>
       </c>
@@ -1313,7 +1239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>24</v>
       </c>
@@ -1339,7 +1265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>25</v>
       </c>
@@ -1365,7 +1291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>26</v>
       </c>
@@ -1391,7 +1317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>21</v>
       </c>
@@ -1417,7 +1343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -1443,7 +1369,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -1469,7 +1395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>11</v>
       </c>
@@ -1495,7 +1421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>9</v>
       </c>
@@ -1521,7 +1447,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -1547,7 +1473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -1573,7 +1499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>25</v>
       </c>
@@ -1599,7 +1525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>25</v>
       </c>
@@ -1622,7 +1548,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>19</v>
       </c>
@@ -1648,7 +1574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>16</v>
       </c>
@@ -1674,7 +1600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -1700,7 +1626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>19</v>
       </c>
@@ -1726,7 +1652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -1752,7 +1678,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>14</v>
       </c>
@@ -1778,7 +1704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>14</v>
       </c>
@@ -1804,7 +1730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>14</v>
       </c>
@@ -1830,7 +1756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>14</v>
       </c>
@@ -1856,7 +1782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>12</v>
       </c>
@@ -1882,7 +1808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>13</v>
       </c>
@@ -1908,7 +1834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>13</v>
       </c>
@@ -1934,7 +1860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>18</v>
       </c>
@@ -1960,7 +1886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>22</v>
       </c>
@@ -1986,7 +1912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>19</v>
       </c>
@@ -2012,7 +1938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>18</v>
       </c>
@@ -2038,7 +1964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>23</v>
       </c>
@@ -2064,7 +1990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>28</v>
       </c>
@@ -2090,7 +2016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>30</v>
       </c>
@@ -2116,7 +2042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>30</v>
       </c>
@@ -2142,7 +2068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>31</v>
       </c>
@@ -2168,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>35</v>
       </c>
@@ -2194,7 +2120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>27</v>
       </c>
@@ -2220,7 +2146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>26</v>
       </c>
@@ -2246,7 +2172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>24</v>
       </c>
@@ -2272,7 +2198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>25</v>
       </c>
@@ -2298,7 +2224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>23</v>
       </c>
@@ -2324,7 +2250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>20</v>
       </c>
@@ -2350,7 +2276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>21</v>
       </c>
@@ -2376,7 +2302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>13</v>
       </c>
@@ -2402,7 +2328,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>14</v>
       </c>
@@ -2428,7 +2354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>15</v>
       </c>
@@ -2454,7 +2380,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>14</v>
       </c>
@@ -2480,7 +2406,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>17</v>
       </c>
@@ -2506,7 +2432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>11</v>
       </c>
@@ -2532,7 +2458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>13</v>
       </c>
@@ -2558,7 +2484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>12</v>
       </c>
@@ -2584,7 +2510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>13</v>
       </c>
@@ -2610,7 +2536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>19</v>
       </c>
@@ -2636,7 +2562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>15</v>
       </c>
@@ -2662,7 +2588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>13</v>
       </c>
@@ -2688,7 +2614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>13</v>
       </c>
@@ -2714,7 +2640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>14</v>
       </c>
@@ -2740,7 +2666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>18</v>
       </c>
@@ -2766,7 +2692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>22</v>
       </c>
@@ -2792,7 +2718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>21</v>
       </c>
@@ -2818,7 +2744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>26</v>
       </c>
@@ -2844,7 +2770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>22</v>
       </c>
@@ -2870,7 +2796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>28</v>
       </c>
@@ -2896,7 +2822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>23</v>
       </c>
@@ -2922,7 +2848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>28</v>
       </c>
@@ -2948,7 +2874,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>27</v>
       </c>
@@ -2974,7 +2900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>13</v>
       </c>
@@ -3000,7 +2926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>14</v>
       </c>
@@ -3026,7 +2952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>13</v>
       </c>
@@ -3052,7 +2978,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>14</v>
       </c>
@@ -3078,7 +3004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>15</v>
       </c>
@@ -3104,7 +3030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>12</v>
       </c>
@@ -3130,7 +3056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>13</v>
       </c>
@@ -3156,7 +3082,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>13</v>
       </c>
@@ -3182,7 +3108,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>14</v>
       </c>
@@ -3208,7 +3134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>13</v>
       </c>
@@ -3234,7 +3160,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>12</v>
       </c>
@@ -3260,7 +3186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>13</v>
       </c>
@@ -3286,7 +3212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>18</v>
       </c>
@@ -3312,7 +3238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>16</v>
       </c>
@@ -3338,7 +3264,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>18</v>
       </c>
@@ -3364,7 +3290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>18</v>
       </c>
@@ -3390,7 +3316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>23</v>
       </c>
@@ -3416,7 +3342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>26</v>
       </c>
@@ -3442,7 +3368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>11</v>
       </c>
@@ -3468,7 +3394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>12</v>
       </c>
@@ -3494,7 +3420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>13</v>
       </c>
@@ -3520,7 +3446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>12</v>
       </c>
@@ -3546,7 +3472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>18</v>
       </c>
@@ -3572,7 +3498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>20</v>
       </c>
@@ -3598,7 +3524,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>21</v>
       </c>
@@ -3624,7 +3550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>22</v>
       </c>
@@ -3650,7 +3576,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>18</v>
       </c>
@@ -3676,7 +3602,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>19</v>
       </c>
@@ -3702,7 +3628,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>21</v>
       </c>
@@ -3728,7 +3654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>26</v>
       </c>
@@ -3754,7 +3680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>15</v>
       </c>
@@ -3780,7 +3706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>16</v>
       </c>
@@ -3806,7 +3732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>29</v>
       </c>
@@ -3832,7 +3758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>24</v>
       </c>
@@ -3858,7 +3784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>20</v>
       </c>
@@ -3884,7 +3810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>19</v>
       </c>
@@ -3910,7 +3836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>15</v>
       </c>
@@ -3936,7 +3862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>24</v>
       </c>
@@ -3962,7 +3888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>20</v>
       </c>
@@ -3988,7 +3914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>11</v>
       </c>
@@ -4014,7 +3940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>20</v>
       </c>
@@ -4040,7 +3966,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>21</v>
       </c>
@@ -4063,7 +3989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>19</v>
       </c>
@@ -4089,7 +4015,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>15</v>
       </c>
@@ -4115,7 +4041,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>31</v>
       </c>
@@ -4141,7 +4067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>26</v>
       </c>
@@ -4167,7 +4093,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>32</v>
       </c>
@@ -4193,7 +4119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>25</v>
       </c>
@@ -4219,7 +4145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>16</v>
       </c>
@@ -4245,7 +4171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>16</v>
       </c>
@@ -4271,7 +4197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>18</v>
       </c>
@@ -4297,7 +4223,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>16</v>
       </c>
@@ -4323,7 +4249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>13</v>
       </c>
@@ -4349,7 +4275,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>14</v>
       </c>
@@ -4375,7 +4301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>14</v>
       </c>
@@ -4401,7 +4327,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>14</v>
       </c>
@@ -4427,7 +4353,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>29</v>
       </c>
@@ -4453,7 +4379,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>26</v>
       </c>
@@ -4479,7 +4405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>26</v>
       </c>
@@ -4505,7 +4431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>31</v>
       </c>
@@ -4531,7 +4457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>32</v>
       </c>
@@ -4557,7 +4483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>28</v>
       </c>
@@ -4583,7 +4509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>24</v>
       </c>
@@ -4609,7 +4535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>26</v>
       </c>
@@ -4635,7 +4561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>24</v>
       </c>
@@ -4661,7 +4587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>26</v>
       </c>
@@ -4687,7 +4613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>31</v>
       </c>
@@ -4713,7 +4639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>19</v>
       </c>
@@ -4739,7 +4665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>18</v>
       </c>
@@ -4765,7 +4691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>15</v>
       </c>
@@ -4791,7 +4717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>15</v>
       </c>
@@ -4817,7 +4743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>16</v>
       </c>
@@ -4843,7 +4769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>15</v>
       </c>
@@ -4869,7 +4795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>16</v>
       </c>
@@ -4895,7 +4821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>14</v>
       </c>
@@ -4921,7 +4847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>17</v>
       </c>
@@ -4947,7 +4873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>16</v>
       </c>
@@ -4973,7 +4899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>15</v>
       </c>
@@ -4999,7 +4925,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>18</v>
       </c>
@@ -5025,7 +4951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>21</v>
       </c>
@@ -5051,7 +4977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>20</v>
       </c>
@@ -5077,7 +5003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>13</v>
       </c>
@@ -5103,7 +5029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>29</v>
       </c>
@@ -5129,7 +5055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>23</v>
       </c>
@@ -5155,7 +5081,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>20</v>
       </c>
@@ -5181,7 +5107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>23</v>
       </c>
@@ -5207,7 +5133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>24</v>
       </c>
@@ -5233,7 +5159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>25</v>
       </c>
@@ -5259,7 +5185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>24</v>
       </c>
@@ -5285,7 +5211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>18</v>
       </c>
@@ -5311,7 +5237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>29</v>
       </c>
@@ -5337,7 +5263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>19</v>
       </c>
@@ -5363,7 +5289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>23</v>
       </c>
@@ -5389,7 +5315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>23</v>
       </c>
@@ -5415,7 +5341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>22</v>
       </c>
@@ -5441,7 +5367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>25</v>
       </c>
@@ -5467,7 +5393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>33</v>
       </c>
@@ -5493,7 +5419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>28</v>
       </c>
@@ -5519,7 +5445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>25</v>
       </c>
@@ -5545,7 +5471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>25</v>
       </c>
@@ -5571,7 +5497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>26</v>
       </c>
@@ -5597,7 +5523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>27</v>
       </c>
@@ -5623,7 +5549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>17.5</v>
       </c>
@@ -5649,7 +5575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>16</v>
       </c>
@@ -5675,7 +5601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>15.5</v>
       </c>
@@ -5701,7 +5627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>14.5</v>
       </c>
@@ -5727,7 +5653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>22</v>
       </c>
@@ -5753,7 +5679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>22</v>
       </c>
@@ -5779,7 +5705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>24</v>
       </c>
@@ -5805,7 +5731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>22.5</v>
       </c>
@@ -5831,7 +5757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>29</v>
       </c>
@@ -5857,7 +5783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>24.5</v>
       </c>
@@ -5883,7 +5809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>29</v>
       </c>
@@ -5909,7 +5835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>33</v>
       </c>
@@ -5935,7 +5861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>20</v>
       </c>
@@ -5961,7 +5887,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>18</v>
       </c>
@@ -5987,7 +5913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>18.5</v>
       </c>
@@ -6013,7 +5939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>17.5</v>
       </c>
@@ -6039,7 +5965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>29.5</v>
       </c>
@@ -6065,7 +5991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>32</v>
       </c>
@@ -6091,7 +6017,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>28</v>
       </c>
@@ -6117,7 +6043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>26.5</v>
       </c>
@@ -6143,7 +6069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>20</v>
       </c>
@@ -6169,7 +6095,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>13</v>
       </c>
@@ -6195,7 +6121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>19</v>
       </c>
@@ -6221,7 +6147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>19</v>
       </c>
@@ -6247,7 +6173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>16.5</v>
       </c>
@@ -6273,7 +6199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>16.5</v>
       </c>
@@ -6299,7 +6225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>13</v>
       </c>
@@ -6325,7 +6251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>13</v>
       </c>
@@ -6351,7 +6277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>13</v>
       </c>
@@ -6377,7 +6303,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>31.5</v>
       </c>
@@ -6403,7 +6329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>30</v>
       </c>
@@ -6429,7 +6355,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>36</v>
       </c>
@@ -6455,7 +6381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>25.5</v>
       </c>
@@ -6481,7 +6407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>33.5</v>
       </c>
@@ -6507,7 +6433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>17.5</v>
       </c>
@@ -6533,7 +6459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>17</v>
       </c>
@@ -6559,7 +6485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>15.5</v>
       </c>
@@ -6585,7 +6511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>15</v>
       </c>
@@ -6611,7 +6537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>17.5</v>
       </c>
@@ -6637,7 +6563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>20.5</v>
       </c>
@@ -6663,7 +6589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>19</v>
       </c>
@@ -6689,7 +6615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>18.5</v>
       </c>
@@ -6715,7 +6641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>16</v>
       </c>
@@ -6741,7 +6667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>15.5</v>
       </c>
@@ -6767,7 +6693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>15.5</v>
       </c>
@@ -6793,7 +6719,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>16</v>
       </c>
@@ -6819,7 +6745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>29</v>
       </c>
@@ -6845,7 +6771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>24.5</v>
       </c>
@@ -6871,7 +6797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>26</v>
       </c>
@@ -6897,7 +6823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>25.5</v>
       </c>
@@ -6923,7 +6849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>30.5</v>
       </c>
@@ -6949,7 +6875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>33.5</v>
       </c>
@@ -6975,7 +6901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>30</v>
       </c>
@@ -7001,7 +6927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>30.5</v>
       </c>
@@ -7027,7 +6953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>22</v>
       </c>
@@ -7053,7 +6979,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>21.5</v>
       </c>
@@ -7079,7 +7005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>21.5</v>
       </c>
@@ -7105,7 +7031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>43.1</v>
       </c>
@@ -7131,7 +7057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>36.1</v>
       </c>
@@ -7157,7 +7083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>32.799999999999997</v>
       </c>
@@ -7183,7 +7109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>39.4</v>
       </c>
@@ -7209,7 +7135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>36.1</v>
       </c>
@@ -7235,7 +7161,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>19.899999999999999</v>
       </c>
@@ -7261,7 +7187,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>19.399999999999999</v>
       </c>
@@ -7287,7 +7213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>20.2</v>
       </c>
@@ -7313,7 +7239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>19.2</v>
       </c>
@@ -7339,7 +7265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>20.5</v>
       </c>
@@ -7365,7 +7291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>20.2</v>
       </c>
@@ -7391,7 +7317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>25.1</v>
       </c>
@@ -7417,7 +7343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>20.5</v>
       </c>
@@ -7443,7 +7369,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>19.399999999999999</v>
       </c>
@@ -7469,7 +7395,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>20.6</v>
       </c>
@@ -7495,7 +7421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>20.8</v>
       </c>
@@ -7521,7 +7447,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>18.600000000000001</v>
       </c>
@@ -7547,7 +7473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>18.100000000000001</v>
       </c>
@@ -7573,7 +7499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>19.2</v>
       </c>
@@ -7599,7 +7525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>17.7</v>
       </c>
@@ -7625,7 +7551,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>18.100000000000001</v>
       </c>
@@ -7651,7 +7577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>17.5</v>
       </c>
@@ -7677,7 +7603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>30</v>
       </c>
@@ -7703,7 +7629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>27.5</v>
       </c>
@@ -7729,7 +7655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>27.2</v>
       </c>
@@ -7755,7 +7681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>30.9</v>
       </c>
@@ -7781,7 +7707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>21.1</v>
       </c>
@@ -7807,7 +7733,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>23.2</v>
       </c>
@@ -7833,7 +7759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>23.8</v>
       </c>
@@ -7859,7 +7785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>23.9</v>
       </c>
@@ -7885,7 +7811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>20.3</v>
       </c>
@@ -7911,7 +7837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>17</v>
       </c>
@@ -7937,7 +7863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>21.6</v>
       </c>
@@ -7963,7 +7889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>16.2</v>
       </c>
@@ -7989,7 +7915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>31.5</v>
       </c>
@@ -8015,7 +7941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>29.5</v>
       </c>
@@ -8041,7 +7967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>21.5</v>
       </c>
@@ -8067,7 +7993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>19.8</v>
       </c>
@@ -8093,7 +8019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>22.3</v>
       </c>
@@ -8119,7 +8045,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>20.2</v>
       </c>
@@ -8145,7 +8071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>20.6</v>
       </c>
@@ -8171,7 +8097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>17</v>
       </c>
@@ -8197,7 +8123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>17.600000000000001</v>
       </c>
@@ -8223,7 +8149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>16.5</v>
       </c>
@@ -8249,7 +8175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>18.2</v>
       </c>
@@ -8275,7 +8201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>16.899999999999999</v>
       </c>
@@ -8301,7 +8227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>15.5</v>
       </c>
@@ -8327,7 +8253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>19.2</v>
       </c>
@@ -8353,7 +8279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>18.5</v>
       </c>
@@ -8379,7 +8305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>31.9</v>
       </c>
@@ -8405,7 +8331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>34.1</v>
       </c>
@@ -8431,7 +8357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>35.700000000000003</v>
       </c>
@@ -8457,7 +8383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>27.4</v>
       </c>
@@ -8483,7 +8409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>25.4</v>
       </c>
@@ -8509,7 +8435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>23</v>
       </c>
@@ -8535,7 +8461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>27.2</v>
       </c>
@@ -8561,7 +8487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>23.9</v>
       </c>
@@ -8587,7 +8513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>34.200000000000003</v>
       </c>
@@ -8613,7 +8539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>34.5</v>
       </c>
@@ -8639,7 +8565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>31.8</v>
       </c>
@@ -8665,7 +8591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>37.299999999999997</v>
       </c>
@@ -8691,7 +8617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>28.4</v>
       </c>
@@ -8717,7 +8643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>28.8</v>
       </c>
@@ -8743,7 +8669,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>26.8</v>
       </c>
@@ -8769,7 +8695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>33.5</v>
       </c>
@@ -8795,7 +8721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>41.5</v>
       </c>
@@ -8821,7 +8747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>38.1</v>
       </c>
@@ -8847,7 +8773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>32.1</v>
       </c>
@@ -8873,7 +8799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>37.200000000000003</v>
       </c>
@@ -8899,7 +8825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>28</v>
       </c>
@@ -8925,7 +8851,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>26.4</v>
       </c>
@@ -8951,7 +8877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>24.3</v>
       </c>
@@ -8977,7 +8903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>19.100000000000001</v>
       </c>
@@ -9003,7 +8929,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>34.299999999999997</v>
       </c>
@@ -9029,7 +8955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>29.8</v>
       </c>
@@ -9055,7 +8981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>31.3</v>
       </c>
@@ -9081,7 +9007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>37</v>
       </c>
@@ -9107,7 +9033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>32.200000000000003</v>
       </c>
@@ -9133,7 +9059,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>46.6</v>
       </c>
@@ -9159,7 +9085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>27.9</v>
       </c>
@@ -9185,7 +9111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>40.799999999999997</v>
       </c>
@@ -9211,7 +9137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>44.3</v>
       </c>
@@ -9237,7 +9163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>43.4</v>
       </c>
@@ -9263,7 +9189,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>36.4</v>
       </c>
@@ -9289,7 +9215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>30</v>
       </c>
@@ -9315,7 +9241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>44.6</v>
       </c>
@@ -9341,7 +9267,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>40.9</v>
       </c>
@@ -9364,7 +9290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>33.799999999999997</v>
       </c>
@@ -9390,7 +9316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>29.8</v>
       </c>
@@ -9416,7 +9342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>32.700000000000003</v>
       </c>
@@ -9442,7 +9368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>23.7</v>
       </c>
@@ -9468,7 +9394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>35</v>
       </c>
@@ -9494,7 +9420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>23.6</v>
       </c>
@@ -9517,7 +9443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>32.4</v>
       </c>
@@ -9543,7 +9469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>27.2</v>
       </c>
@@ -9569,7 +9495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>26.6</v>
       </c>
@@ -9595,7 +9521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>25.8</v>
       </c>
@@ -9621,7 +9547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>23.5</v>
       </c>
@@ -9647,7 +9573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>30</v>
       </c>
@@ -9673,7 +9599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>39.1</v>
       </c>
@@ -9699,7 +9625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>39</v>
       </c>
@@ -9725,7 +9651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>35.1</v>
       </c>
@@ -9751,7 +9677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>32.299999999999997</v>
       </c>
@@ -9777,7 +9703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>37</v>
       </c>
@@ -9803,7 +9729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>37.700000000000003</v>
       </c>
@@ -9829,7 +9755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>34.1</v>
       </c>
@@ -9855,7 +9781,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>34.700000000000003</v>
       </c>
@@ -9881,7 +9807,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>34.4</v>
       </c>
@@ -9907,7 +9833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>29.9</v>
       </c>
@@ -9933,7 +9859,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>33</v>
       </c>
@@ -9959,7 +9885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>34.5</v>
       </c>
@@ -9982,7 +9908,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>33.700000000000003</v>
       </c>
@@ -10008,7 +9934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>32.4</v>
       </c>
@@ -10034,7 +9960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>32.9</v>
       </c>
@@ -10060,7 +9986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>31.6</v>
       </c>
@@ -10086,7 +10012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>28.1</v>
       </c>
@@ -10112,7 +10038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>30.7</v>
       </c>
@@ -10138,7 +10064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>25.4</v>
       </c>
@@ -10164,7 +10090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>24.2</v>
       </c>
@@ -10190,7 +10116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>22.4</v>
       </c>
@@ -10216,7 +10142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>26.6</v>
       </c>
@@ -10242,7 +10168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>20.2</v>
       </c>
@@ -10268,7 +10194,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>17.600000000000001</v>
       </c>
@@ -10294,7 +10220,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>28</v>
       </c>
@@ -10320,7 +10246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>27</v>
       </c>
@@ -10346,7 +10272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>34</v>
       </c>
@@ -10372,7 +10298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>31</v>
       </c>
@@ -10398,7 +10324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>29</v>
       </c>
@@ -10424,7 +10350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>27</v>
       </c>
@@ -10450,7 +10376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>24</v>
       </c>
@@ -10476,7 +10402,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>23</v>
       </c>
@@ -10499,7 +10425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>36</v>
       </c>
@@ -10525,7 +10451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>37</v>
       </c>
@@ -10551,7 +10477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>31</v>
       </c>
@@ -10577,7 +10503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>38</v>
       </c>
@@ -10603,7 +10529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>36</v>
       </c>
@@ -10629,7 +10555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>36</v>
       </c>
@@ -10655,7 +10581,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>36</v>
       </c>
@@ -10681,7 +10607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>34</v>
       </c>
@@ -10707,7 +10633,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>38</v>
       </c>
@@ -10733,7 +10659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>32</v>
       </c>
@@ -10759,7 +10685,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>38</v>
       </c>
@@ -10785,7 +10711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>25</v>
       </c>
@@ -10811,7 +10737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>38</v>
       </c>
@@ -10837,7 +10763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>26</v>
       </c>
@@ -10863,7 +10789,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>22</v>
       </c>
@@ -10889,7 +10815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>32</v>
       </c>
@@ -10915,7 +10841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>36</v>
       </c>
@@ -10941,7 +10867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>27</v>
       </c>
@@ -10967,7 +10893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>27</v>
       </c>
@@ -10993,7 +10919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>44</v>
       </c>
@@ -11019,7 +10945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>32</v>
       </c>
@@ -11045,7 +10971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>28</v>
       </c>
@@ -11071,7 +10997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>31</v>
       </c>
